--- a/InfoTabloServer/bin/Debug/net6.0/Raspisanie/_6_11_feb.xlsx
+++ b/InfoTabloServer/bin/Debug/net6.0/Raspisanie/_6_11_feb.xlsx
@@ -1277,14 +1277,504 @@
     <x:t>Четверг</x:t>
   </x:si>
   <x:si>
+    <x:t>1. Литература Мякушина И.В. 
+Производственный корпус-Аудитория 45</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. Экономика  Умирова А.Н. 
+Основной корпус-Аудитория 202</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1. </x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. Обществознание Нургалеева И.Ю. 
+Основной корпус-Актовый зал</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. История Швиндина Н.А. 
+Основной корпус-Аудитория 201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. Астрономия Колотвина М.Г. 
+Основной корпус-Аудитория 313</x:t>
+  </x:si>
+  <x:si>
+    <x:t>МДК 01.03 Международные расчеты по экспортно-импортным операциям 
+Лопатина М.М. 
+Производственный корпус-Аудитория 37</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. Финансы,денежное обращение и кредит 
+Крамаренко Т.С. 
+Производственный корпус-Аудитория 24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Русский язык и культура речи 
+Илюсизова А.А. 
+Основной корпус-Аудитория 302</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Иностранный язык в профессиональной деятельности 
+Кондратьева М.А. 
+Основной корпус-Аудитория 304</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Инженерно-техническая поддержка сопровождения ИС 
+Гиниятулина Н.В. 
+Основной корпус-Аудитория 407</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. МДК.01.02 Организация, принципы построения и функционирования компьютерных сетей Плотникова Ю.А. 
+Основной корпус-Аудитория 405</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. МДК 02.02  Учет кредитых операций банка 
+Силкина М.Г. 
+Производственный корпус-Аудитория 38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Тестирование информационных систем 
+Першин А.В. 
+Основной корпус-Аудитория 207</x:t>
+  </x:si>
+  <x:si>
+    <x:t>МДК.01.02 Поддержка и тестирование программных модулей  
+Малышев А.О. 
+Основной корпус-Аудитория 404</x:t>
+  </x:si>
+  <x:si>
+    <x:t>УП.03.01 Учебная практика 
+Парасовченко Г.И. 
+Основной корпус-Аудитория 402</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2. История Мунасыпова К.Р. 
+Основной корпус-Аудитория 303</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.</x:t>
+  </x:si>
+  <x:si>
     <x:t>География 
 Мязина А.А. 
 Основной корпус-Аудитория 202</x:t>
   </x:si>
   <x:si>
-    <x:t>Обществознание 
-Нургалеева И.Ю. 
+    <x:t>2. Обществознание Карякина Е.Н. 
+Производственный корпус-Аудитория 49Б</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2. Математика 
+Паламарчук И.В. 
+Производственный корпус-О124</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2. История 
+Швиндина Н.А. 
+Основной корпус-Аудитория 201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2. Математика 
+Трушина И.Ю. 
+Производственный корпус-Аудитория 34</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2. Информатика  Коршиков Д.С. 
+Основной корпус-Аудитория 308</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2. Литература Мякушина И.В. 
+Производственный корпус-Аудитория 45</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2. Обществознание Нургалеева И.Ю. 
 Основной корпус-Актовый зал</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2. Русский язык Лыжина Л.А. 
+Производственный корпус-Аудитория 25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2. МДК 01.01 Организация безналичных расчетов 
+Лопатина М.М. 
+Производственный корпус-Аудитория 37</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Основы алгоритмизации и программирования 
+Егурнова Е.Н. 
+Основной корпус-Аудитория 409</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2. Архитектура аппаратных средств 
+Колотвина М.Г. 
+Основной корпус-Аудитория 313</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2. Операционные системы и среды 
+Селищева О.И. 
+Основной корпус-Аудитория 107</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2. ДОП (Раудина О.В.) 209</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2. МДК 02.02  Учет кредитых операций банка 
+Силкина М.Г. 
+Производственный корпус-Аудитория 38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2. МДК.02.02 Программное обеспечение компьютерных сетей 
+Плотникова Ю.А. 
+Основной корпус-Аудитория 405</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2. МДК.03.01 Эксплуатация объектов сетевой инфраструктуры  Сагдиев Т.Ф. 
+Производственный корпус-Аудитория 47</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> </x:t>
+  </x:si>
+  <x:si>
+    <x:t>3. Литература Мякушина И.В. 
+Производственный корпус-Аудитория 45</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3. ОБЖ Чебрукова Т.А. 
+Основной корпус-Аудитория 102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3. Экономика  Умирова А.Н. 
+Основной корпус-Аудитория 302</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3. Обществознание Нургалеева И.Ю. 
+Основной корпус-Аудитория 202</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3. История Швиндина Н.А. 
+Основной корпус-Аудитория 201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3. ДОП (Дубская Е.С.) 410</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3. Физика Колотвина М.Г. 
+Основной корпус-Аудитория 313</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3. МДК.01.02 Кассовые операции банка 
+Крамаренко Т.С. 
+Производственный корпус-Аудитория 24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Статистика 
+Носова Ю.В. 
+Производственный корпус-О124</x:t>
+  </x:si>
+  <x:si>
+    <x:t>МДК 05.02 Разработка кода информационных систем 
+Бикимов А.Ж. 
+Основной корпус-Актовый зал</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Основы проектирования баз данных 
+Гиниятулина Н.В. 
+Основной корпус-Аудитория 308</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3. Операционные системы и среды 
+Селищева О.И. 
+Основной корпус-Аудитория 107</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3. МДК.01.02 Организация, принципы построения и функционирования компьютерных сетей Плотникова Ю.А. 
+Основной корпус-Аудитория 405</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3. МДК 02.02  Учет кредитых операций банка 
+Лопатина М.М. 
+Производственный корпус-Аудитория 37</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3. Информационные технологии в профессиональной деятельности 
+Беляев А.А. 
+Основной корпус-Аудитория 209</x:t>
+  </x:si>
+  <x:si>
+    <x:t>МДК 02.01 Практические основы бухгалтерского учета активов организации  
+Саликова М.А. 
+Производственный корпус-Аудитория 33</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3. МДК.02.01 Администрирование сетевых операционных систем 
+Парасовченко Г.И. 
+Основной корпус-Аудитория 306</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3. МДК.03.01 Эксплуатация объектов сетевой инфраструктуры  Сагдиев Т.Ф. 
+Производственный корпус-Аудитория 47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4. История Мунасыпова К.Р. 
+Основной корпус-Аудитория 303</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4. ОБЖ Чебрукова Т.А. 
+Основной корпус-Аудитория 102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Информатика  Коршиков Д.С. 
+4. Производственный корпус-Аудитория 25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4. Русский язык Мякушина И.В. 
+Производственный корпус-Аудитория 45</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Физика 
+Имашева К.Б. 
+Основной корпус-Аудитория 305</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4. История Швиндина Н.А. 
+Основной корпус-Аудитория 201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4. Русский язык Лыжина Л.А. 
+Производственный корпус-Аудитория 25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Основы предпринимательской деятельности 
+Криворучко А.В. 
+Производственный корпус-Аудитория 37а</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4. Архитектура аппаратных средств 
+Колотвина М.Г. 
+Основной корпус-Аудитория 313</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4. Основы страхования 
+Крамаренко Т.С. 
+Производственный корпус-Аудитория 24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>МДК 04.01 Технология составления бухгалтерской отчетности  
+Умирова А.Н. 
+Основной корпус-Аудитория 302</x:t>
+  </x:si>
+  <x:si>
+    <x:t>МДК.02.01 Технология разработки программного обеспечения 
+Землянская К.В. 
+Основной корпус-Аудитория 407</x:t>
+  </x:si>
+  <x:si>
+    <x:t>МДК.01.01 Разработка программных модулей 
+Егурнова Е.Н. 
+Основной корпус-Аудитория 409</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">4. </x:t>
+  </x:si>
+  <x:si>
+    <x:t>4. МДК.03.01 Эксплуатация объектов сетевой инфраструктуры  Сагдиев Т.Ф. 
+Производственный корпус-Аудитория 47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Тестирование информационных систем 
+Першин А.В. 
+Основной корпус-Аудитория 402</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Управление проектами 
+Андреева Л.В. 
+Основной корпус-Аудитория 410</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Системное программирование 
+Балакин О.Д. 
+Основной корпус-Аудитория 404</x:t>
+  </x:si>
+  <x:si>
+    <x:t>МДК.01.02 Поддержка и тестирование программных модулей  
+Малышев А.О. 
+Основной корпус-Аудитория 308</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4. МДК.03.02 Безопасность компьютерных сетей 
+Плотникова Ю.А. 
+Основной корпус-Аудитория 405</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Информатика  
+Коршиков Д.С. 
+Основной корпус-Аудитория 313</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5. Рынок ценных бумаг 
+Лопатина М.М. 
+Производственный корпус-Аудитория 37</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5. МДК.02.01 Администрирование сетевых операционных систем 
+Парасовченко Г.И. 
+Основной корпус-Аудитория 306</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Теория вероятностей и математическая статистика 
+Синельникова К.С. 
+Основной корпус-Аудитория 102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6. МДК.02.03 Организация администрирования комьютерных систем 
+Парасовченко Г.И. 
+Основной корпус-Аудитория 306</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Тестирование информационных систем 
+Першин А.В. 
+Основной корпус-Аудитория 410</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Пятница</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Иностранный язык 
+Боровцова Е.В. 
+Производственный корпус-Аудитория 37а</x:t>
+  </x:si>
+  <x:si>
+    <x:t>МДК.01.02 Кассовые операции банка 
+Крамаренко Т.С. 
+Производственный корпус-Аудитория 24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Информационные технологии 
+Калиберда Е.Л. 
+Основной корпус-Аудитория 402</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Основы теории информации 
+Землянская К.В. 
+Производственный корпус-Аудитория 47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Теория вероятностей и математическая статистика 
+Жеколдина Р.Р. 
+Производственный корпус-Аудитория 28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Экономика  
+Белан В.Е. 
+Основной корпус-Аудитория 311</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Иностранный язык 
+Сергеева Н.В. 
+Производственный корпус-Аудитория 35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Финансы,денежное обращение и кредит 
+Крамаренко Т.С. 
+Производственный корпус-Аудитория 24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Экономика организации 
+Кравченко С.О. 
+Основной корпус-Аудитория 304</x:t>
+  </x:si>
+  <x:si>
+    <x:t>МДК 06.03 Устройство и функционирование информационной системы 
+Муфазалова Ж.Б. 
+Основной корпус-Аудитория 308</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Статистика 
+Носова Ю.В. 
+Производственный корпус-Аудитория 28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>МДК 05.01 Выполнение работ по профессии "Кассир" 
+Балышева Е.В. 
+Основной корпус-Аудитория 404</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Основы проектирования баз данных 
+Лукьяненко О.В. 
+Основной корпус-Актовый зал</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Основы алгоритмизации и программирования 
+Землянская К.В. 
+Основной корпус-Аудитория 313</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Теория вероятностей и математическая статистика 
+Жеколдина Р.Р. 
+Основной корпус-Аудитория 202</x:t>
+  </x:si>
+  <x:si>
+    <x:t>МДК.05.01 Организация и планирование налоговой деятельности КР 
+Зверева О.М. 
+Производственный корпус-Аудитория 31</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Информатика  
+Коршиков Д.С. 
+Основной корпус-Аудитория 409</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Музыкальная литература 
+Мунасыпова К.Р. 
+Основной корпус-Аудитория 303</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Астрономия 
+Имашева К.Б. 
+Основной корпус-Аудитория 305</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ДОП (Першин А.В.) 407</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Иностранный язык в профессиональной деятельности 
+Сергеева Н.В. 
+Основной корпус-Аудитория 107</x:t>
+  </x:si>
+  <x:si>
+    <x:t>МДК.02.02 Инструментальные средства разработки программного обеспечения 
+Андреева Л.В. 
+Основной корпус-Актовый зал</x:t>
+  </x:si>
+  <x:si>
+    <x:t>МДК 05.02 Разработка кода информационных систем 
+Селищева О.И. 
+Основной корпус-Аудитория 308</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Иностранный язык в профессиональной деятельности 
+Сергеева Н.В. 
+Основной корпус-Аудитория 201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>МДК 05.02 Разработка кода информационных систем 
+Вареников Л.А. 
+Основной корпус-Аудитория 409</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Суббота</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Иностранный язык 
+Сергеева Н.В. 
+Основной корпус-Аудитория 102</x:t>
   </x:si>
   <x:si>
     <x:t>Астрономия 
@@ -1293,302 +1783,13 @@
   </x:si>
   <x:si>
     <x:t>МДК 01.03 Международные расчеты по экспортно-импортным операциям 
-Лопатина М.М. 
-Производственный корпус-Аудитория 37</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Русский язык и культура речи 
-Илюсизова А.А. 
-Основной корпус-Аудитория 302</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Иностранный язык в профессиональной деятельности 
-Кондратьева М.А. 
-Основной корпус-Аудитория 304</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Инженерно-техническая поддержка сопровождения ИС 
-Гиниятулина Н.В. 
-Основной корпус-Аудитория 407</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Тестирование информационных систем 
-Першин А.В. 
-Основной корпус-Аудитория 207</x:t>
-  </x:si>
-  <x:si>
-    <x:t>МДК.01.02 Поддержка и тестирование программных модулей  
-Малышев А.О. 
-Основной корпус-Аудитория 404</x:t>
-  </x:si>
-  <x:si>
-    <x:t>УП.03.01 Учебная практика 
-Парасовченко Г.И. 
-Основной корпус-Аудитория 402</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Иностранный язык 
-Боровцова Е.В. 
-Производственный корпус-Аудитория 37а</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Информатика  
-Бухарова Э.Э. 
-Основной корпус-Аудитория 308</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Основы алгоритмизации и программирования 
-Егурнова Е.Н. 
-Основной корпус-Аудитория 409</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Операционные системы и среды 
-Селищева О.И. 
-Основной корпус-Аудитория 107</x:t>
-  </x:si>
-  <x:si>
-    <x:t>МДК 02.02  Учет кредитых операций банка 
 Силкина М.Г. 
 Производственный корпус-Аудитория 38</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Информатика  
-Бухарова Э.Э. 
-Основной корпус-Аудитория 402</x:t>
-  </x:si>
-  <x:si>
-    <x:t>МДК.01.02 Кассовые операции банка 
-Крамаренко Т.С. 
-Производственный корпус-Аудитория 24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Статистика 
-Носова Ю.В. 
-Производственный корпус-О124</x:t>
-  </x:si>
-  <x:si>
-    <x:t>МДК 05.02 Разработка кода информационных систем 
-Бикимов А.Ж. 
-Основной корпус-Актовый зал</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Основы проектирования баз данных 
-Гиниятулина Н.В. 
-Основной корпус-Аудитория 308</x:t>
-  </x:si>
-  <x:si>
-    <x:t>МДК 02.02  Учет кредитых операций банка 
-Лопатина М.М. 
-Производственный корпус-Аудитория 37</x:t>
   </x:si>
   <x:si>
     <x:t>Информационные технологии в профессиональной деятельности 
 Беляев А.А. 
 Основной корпус-Аудитория 209</x:t>
-  </x:si>
-  <x:si>
-    <x:t>МДК 02.01 Практические основы бухгалтерского учета активов организации  
-Саликова М.А. 
-Производственный корпус-Аудитория 33</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Информатика  
-Коршиков Д.С. 
-Производственный корпус-Аудитория 25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Физика 
-Имашева К.Б. 
-Основной корпус-Аудитория 305</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Финансы,денежное обращение и кредит 
-Крамаренко Т.С. 
-Производственный корпус-Аудитория 24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Основы предпринимательской деятельности 
-Криворучко А.В. 
-Производственный корпус-Аудитория 37а</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Иностранный язык в профессиональной деятельности 
-Боровцова Е.В. 
-Производственный корпус-Аудитория 23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>МДК 04.01 Технология составления бухгалтерской отчетности  
-Умирова А.Н. 
-Основной корпус-Аудитория 302</x:t>
-  </x:si>
-  <x:si>
-    <x:t>МДК.02.01 Технология разработки программного обеспечения 
-Землянская К.В. 
-Основной корпус-Аудитория 407</x:t>
-  </x:si>
-  <x:si>
-    <x:t>МДК.01.01 Разработка программных модулей 
-Егурнова Е.Н. 
-Основной корпус-Аудитория 409</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Тестирование информационных систем 
-Першин А.В. 
-Основной корпус-Аудитория 402</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Управление проектами 
-Андреева Л.В. 
-Основной корпус-Аудитория 410</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Системное программирование 
-Балакин О.Д. 
-Основной корпус-Аудитория 404</x:t>
-  </x:si>
-  <x:si>
-    <x:t>МДК.01.02 Поддержка и тестирование программных модулей  
-Малышев А.О. 
-Основной корпус-Аудитория 308</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Информатика  
-Коршиков Д.С. 
-Основной корпус-Аудитория 313</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Теория вероятностей и математическая статистика 
-Синельникова К.С. 
-Основной корпус-Аудитория 102</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Тестирование информационных систем 
-Першин А.В. 
-Основной корпус-Аудитория 410</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Пятница</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Информационные технологии 
-Калиберда Е.Л. 
-Основной корпус-Аудитория 402</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Основы теории информации 
-Землянская К.В. 
-Производственный корпус-Аудитория 47</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Теория вероятностей и математическая статистика 
-Жеколдина Р.Р. 
-Производственный корпус-Аудитория 28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Экономика  
-Белан В.Е. 
-Основной корпус-Аудитория 311</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Иностранный язык 
-Сергеева Н.В. 
-Производственный корпус-Аудитория 35</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Экономика организации 
-Кравченко С.О. 
-Основной корпус-Аудитория 304</x:t>
-  </x:si>
-  <x:si>
-    <x:t>МДК 06.03 Устройство и функционирование информационной системы 
-Муфазалова Ж.Б. 
-Основной корпус-Аудитория 308</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Статистика 
-Носова Ю.В. 
-Производственный корпус-Аудитория 28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>МДК 05.01 Выполнение работ по профессии "Кассир" 
-Балышева Е.В. 
-Основной корпус-Аудитория 404</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Основы проектирования баз данных 
-Лукьяненко О.В. 
-Основной корпус-Актовый зал</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Основы алгоритмизации и программирования 
-Землянская К.В. 
-Основной корпус-Аудитория 313</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Теория вероятностей и математическая статистика 
-Жеколдина Р.Р. 
-Основной корпус-Аудитория 202</x:t>
-  </x:si>
-  <x:si>
-    <x:t>МДК.05.01 Организация и планирование налоговой деятельности КР 
-Зверева О.М. 
-Производственный корпус-Аудитория 31</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Информатика  
-Коршиков Д.С. 
-Основной корпус-Аудитория 409</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Музыкальная литература 
-Мунасыпова К.Р. 
-Основной корпус-Аудитория 303</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Астрономия 
-Имашева К.Б. 
-Основной корпус-Аудитория 305</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ДОП (Першин А.В.) 407</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Иностранный язык в профессиональной деятельности 
-Сергеева Н.В. 
-Основной корпус-Аудитория 107</x:t>
-  </x:si>
-  <x:si>
-    <x:t>МДК.02.02 Инструментальные средства разработки программного обеспечения 
-Андреева Л.В. 
-Основной корпус-Актовый зал</x:t>
-  </x:si>
-  <x:si>
-    <x:t>МДК 05.02 Разработка кода информационных систем 
-Селищева О.И. 
-Основной корпус-Аудитория 308</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Иностранный язык в профессиональной деятельности 
-Сергеева Н.В. 
-Основной корпус-Аудитория 201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>МДК 05.02 Разработка кода информационных систем 
-Вареников Л.А. 
-Основной корпус-Аудитория 409</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Суббота</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Иностранный язык 
-Сергеева Н.В. 
-Основной корпус-Аудитория 102</x:t>
-  </x:si>
-  <x:si>
-    <x:t>МДК 01.03 Международные расчеты по экспортно-импортным операциям 
-Силкина М.Г. 
-Производственный корпус-Аудитория 38</x:t>
   </x:si>
   <x:si>
     <x:t>Иностранный язык 
@@ -2962,7 +3163,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{59d8a3d0-7b28-4a5e-9e84-af0dd7715481}" mc:Ignorable="x14ac xr xr2 xr3">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{2fdb14e8-66f3-4b14-bdbd-a0d5a6690c4b}" mc:Ignorable="x14ac xr xr2 xr3">
   <x:sheetPr codeName="Лист1">
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -3017,6 +3218,29 @@
       <x:c r="AK1" s="0"/>
       <x:c r="AL1" s="0"/>
       <x:c r="AM1" s="0"/>
+      <x:c r="AN1" s="0"/>
+      <x:c r="AO1" s="0"/>
+      <x:c r="AP1" s="0"/>
+      <x:c r="AQ1" s="0"/>
+      <x:c r="AR1" s="0"/>
+      <x:c r="AS1" s="0"/>
+      <x:c r="AT1" s="0"/>
+      <x:c r="AU1" s="0"/>
+      <x:c r="AV1" s="0"/>
+      <x:c r="AW1" s="0"/>
+      <x:c r="AX1" s="0"/>
+      <x:c r="AY1" s="0"/>
+      <x:c r="AZ1" s="0"/>
+      <x:c r="BA1" s="0"/>
+      <x:c r="BB1" s="0"/>
+      <x:c r="BC1" s="0"/>
+      <x:c r="BD1" s="0"/>
+      <x:c r="BE1" s="0"/>
+      <x:c r="BF1" s="0"/>
+      <x:c r="BG1" s="0"/>
+      <x:c r="BH1" s="0"/>
+      <x:c r="BI1" s="0"/>
+      <x:c r="BJ1" s="0"/>
     </x:row>
     <x:row r="2" spans="1:62" s="29" customFormat="1" ht="12" customHeight="1">
       <x:c r="A2" s="30"/>
@@ -3055,6 +3279,36 @@
       <x:c r="AD2" s="31"/>
       <x:c r="AE2" s="31"/>
       <x:c r="AF2" s="31"/>
+      <x:c r="AG2" s="29"/>
+      <x:c r="AH2" s="29"/>
+      <x:c r="AI2" s="29"/>
+      <x:c r="AJ2" s="29"/>
+      <x:c r="AK2" s="29"/>
+      <x:c r="AL2" s="29"/>
+      <x:c r="AM2" s="29"/>
+      <x:c r="AN2" s="29"/>
+      <x:c r="AO2" s="29"/>
+      <x:c r="AP2" s="29"/>
+      <x:c r="AQ2" s="29"/>
+      <x:c r="AR2" s="29"/>
+      <x:c r="AS2" s="29"/>
+      <x:c r="AT2" s="29"/>
+      <x:c r="AU2" s="29"/>
+      <x:c r="AV2" s="29"/>
+      <x:c r="AW2" s="29"/>
+      <x:c r="AX2" s="29"/>
+      <x:c r="AY2" s="29"/>
+      <x:c r="AZ2" s="29"/>
+      <x:c r="BA2" s="29"/>
+      <x:c r="BB2" s="29"/>
+      <x:c r="BC2" s="29"/>
+      <x:c r="BD2" s="29"/>
+      <x:c r="BE2" s="29"/>
+      <x:c r="BF2" s="29"/>
+      <x:c r="BG2" s="29"/>
+      <x:c r="BH2" s="29"/>
+      <x:c r="BI2" s="29"/>
+      <x:c r="BJ2" s="29"/>
     </x:row>
     <x:row r="3" spans="1:62" s="29" customFormat="1" ht="18" customHeight="1">
       <x:c r="A3" s="30"/>
@@ -3091,6 +3345,36 @@
       <x:c r="AD3" s="34"/>
       <x:c r="AE3" s="34"/>
       <x:c r="AF3" s="34"/>
+      <x:c r="AG3" s="29"/>
+      <x:c r="AH3" s="29"/>
+      <x:c r="AI3" s="29"/>
+      <x:c r="AJ3" s="29"/>
+      <x:c r="AK3" s="29"/>
+      <x:c r="AL3" s="29"/>
+      <x:c r="AM3" s="29"/>
+      <x:c r="AN3" s="29"/>
+      <x:c r="AO3" s="29"/>
+      <x:c r="AP3" s="29"/>
+      <x:c r="AQ3" s="29"/>
+      <x:c r="AR3" s="29"/>
+      <x:c r="AS3" s="29"/>
+      <x:c r="AT3" s="29"/>
+      <x:c r="AU3" s="29"/>
+      <x:c r="AV3" s="29"/>
+      <x:c r="AW3" s="29"/>
+      <x:c r="AX3" s="29"/>
+      <x:c r="AY3" s="29"/>
+      <x:c r="AZ3" s="29"/>
+      <x:c r="BA3" s="29"/>
+      <x:c r="BB3" s="29"/>
+      <x:c r="BC3" s="29"/>
+      <x:c r="BD3" s="29"/>
+      <x:c r="BE3" s="29"/>
+      <x:c r="BF3" s="29"/>
+      <x:c r="BG3" s="29"/>
+      <x:c r="BH3" s="29"/>
+      <x:c r="BI3" s="29"/>
+      <x:c r="BJ3" s="29"/>
     </x:row>
     <x:row r="4" spans="1:62" s="29" customFormat="1" ht="12.75" customHeight="1">
       <x:c r="A4" s="30"/>
@@ -3125,6 +3409,36 @@
       <x:c r="AD4" s="34"/>
       <x:c r="AE4" s="34"/>
       <x:c r="AF4" s="34"/>
+      <x:c r="AG4" s="29"/>
+      <x:c r="AH4" s="29"/>
+      <x:c r="AI4" s="29"/>
+      <x:c r="AJ4" s="29"/>
+      <x:c r="AK4" s="29"/>
+      <x:c r="AL4" s="29"/>
+      <x:c r="AM4" s="29"/>
+      <x:c r="AN4" s="29"/>
+      <x:c r="AO4" s="29"/>
+      <x:c r="AP4" s="29"/>
+      <x:c r="AQ4" s="29"/>
+      <x:c r="AR4" s="29"/>
+      <x:c r="AS4" s="29"/>
+      <x:c r="AT4" s="29"/>
+      <x:c r="AU4" s="29"/>
+      <x:c r="AV4" s="29"/>
+      <x:c r="AW4" s="29"/>
+      <x:c r="AX4" s="29"/>
+      <x:c r="AY4" s="29"/>
+      <x:c r="AZ4" s="29"/>
+      <x:c r="BA4" s="29"/>
+      <x:c r="BB4" s="29"/>
+      <x:c r="BC4" s="29"/>
+      <x:c r="BD4" s="29"/>
+      <x:c r="BE4" s="29"/>
+      <x:c r="BF4" s="29"/>
+      <x:c r="BG4" s="29"/>
+      <x:c r="BH4" s="29"/>
+      <x:c r="BI4" s="29"/>
+      <x:c r="BJ4" s="29"/>
     </x:row>
     <x:row r="5" spans="1:62" s="7" customFormat="1" ht="24.6" customHeight="1">
       <x:c r="A5" s="35" t="s">
@@ -5652,10 +5966,10 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="C24" s="44" t="s">
-        <x:v>184</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="D24" s="44" t="s">
-        <x:v>122</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="E24" s="44" t="s">
         <x:v>70</x:v>
@@ -5664,20 +5978,22 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="G24" s="44" t="s">
-        <x:v>286</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="H24" s="44" t="s">
-        <x:v>286</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="I24" s="44" t="s">
-        <x:v>287</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="J24" s="44" t="s">
-        <x:v>287</x:v>
-      </x:c>
-      <x:c r="K24" s="44"/>
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="K24" s="44" t="s">
+        <x:v>289</x:v>
+      </x:c>
       <x:c r="L24" s="44" t="s">
-        <x:v>83</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="M24" s="44" t="s">
         <x:v>76</x:v>
@@ -5691,37 +6007,39 @@
       <x:c r="P24" s="44"/>
       <x:c r="Q24" s="44"/>
       <x:c r="R24" s="44" t="s">
-        <x:v>68</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="S24" s="44" t="s">
-        <x:v>82</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="T24" s="44" t="s">
-        <x:v>123</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="U24" s="44" t="s">
-        <x:v>288</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="V24" s="44" t="s">
-        <x:v>289</x:v>
-      </x:c>
-      <x:c r="W24" s="44"/>
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="W24" s="44" t="s">
+        <x:v>294</x:v>
+      </x:c>
       <x:c r="X24" s="44" t="s">
         <x:v>223</x:v>
       </x:c>
       <x:c r="Y24" s="44" t="s">
-        <x:v>290</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="Z24" s="44"/>
       <x:c r="AA24" s="44" t="s">
-        <x:v>291</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="AB24" s="44" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="AC24" s="44"/>
       <x:c r="AD24" s="44" t="s">
-        <x:v>292</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="AE24" s="44" t="s">
         <x:v>89</x:v>
@@ -5730,13 +6048,19 @@
       <x:c r="AG24" s="44" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="AH24" s="44"/>
+      <x:c r="AH24" s="44" t="s">
+        <x:v>298</x:v>
+      </x:c>
       <x:c r="AI24" s="44" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="AJ24" s="44"/>
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="AJ24" s="44" t="s">
+        <x:v>289</x:v>
+      </x:c>
       <x:c r="AK24" s="44"/>
-      <x:c r="AL24" s="44"/>
+      <x:c r="AL24" s="44" t="s">
+        <x:v>299</x:v>
+      </x:c>
       <x:c r="AM24" s="44"/>
       <x:c r="AN24" s="44"/>
       <x:c r="AO24" s="44"/>
@@ -5752,24 +6076,30 @@
       <x:c r="AU24" s="44"/>
       <x:c r="AV24" s="44"/>
       <x:c r="AW24" s="44"/>
-      <x:c r="AX24" s="44"/>
-      <x:c r="AY24" s="44"/>
+      <x:c r="AX24" s="44" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="AY24" s="44" t="s">
+        <x:v>287</x:v>
+      </x:c>
       <x:c r="AZ24" s="44"/>
       <x:c r="BA24" s="44"/>
       <x:c r="BB24" s="44" t="s">
-        <x:v>293</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="BC24" s="44"/>
       <x:c r="BD24" s="44"/>
       <x:c r="BE24" s="44"/>
       <x:c r="BF24" s="44"/>
       <x:c r="BG24" s="44" t="s">
-        <x:v>294</x:v>
-      </x:c>
-      <x:c r="BH24" s="44"/>
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="BH24" s="44" t="s">
+        <x:v>287</x:v>
+      </x:c>
       <x:c r="BI24" s="44"/>
       <x:c r="BJ24" s="44" t="s">
-        <x:v>295</x:v>
+        <x:v>302</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:62" ht="63.75" customHeight="1">
@@ -5778,34 +6108,34 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="C25" s="44" t="s">
-        <x:v>122</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="D25" s="44" t="s">
-        <x:v>68</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="E25" s="44" t="s">
-        <x:v>286</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="F25" s="44" t="s">
-        <x:v>286</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="G25" s="44" t="s">
-        <x:v>78</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="H25" s="44" t="s">
-        <x:v>70</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="I25" s="44" t="s">
-        <x:v>82</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="J25" s="44" t="s">
-        <x:v>208</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="K25" s="44" t="s">
-        <x:v>296</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="L25" s="44" t="s">
-        <x:v>184</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="M25" s="44" t="s">
         <x:v>102</x:v>
@@ -5821,22 +6151,22 @@
       </x:c>
       <x:c r="Q25" s="44"/>
       <x:c r="R25" s="44" t="s">
-        <x:v>287</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="S25" s="44" t="s">
-        <x:v>287</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="T25" s="44" t="s">
-        <x:v>297</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="U25" s="44" t="s">
-        <x:v>123</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="V25" s="44" t="s">
         <x:v>71</x:v>
       </x:c>
       <x:c r="W25" s="44" t="s">
-        <x:v>195</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="X25" s="44" t="s">
         <x:v>198</x:v>
@@ -5860,26 +6190,26 @@
         <x:v>272</x:v>
       </x:c>
       <x:c r="AE25" s="44" t="s">
-        <x:v>292</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="AF25" s="44" t="s">
-        <x:v>298</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="AG25" s="44" t="s">
         <x:v>129</x:v>
       </x:c>
       <x:c r="AH25" s="44" t="s">
-        <x:v>254</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="AI25" s="44" t="s">
-        <x:v>299</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="AJ25" s="46" t="s">
-        <x:v>217</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="AK25" s="44"/>
       <x:c r="AL25" s="44" t="s">
-        <x:v>300</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="AM25" s="44"/>
       <x:c r="AN25" s="44"/>
@@ -5898,14 +6228,16 @@
       <x:c r="AU25" s="44"/>
       <x:c r="AV25" s="44"/>
       <x:c r="AW25" s="44"/>
-      <x:c r="AX25" s="44"/>
+      <x:c r="AX25" s="44" t="s">
+        <x:v>304</x:v>
+      </x:c>
       <x:c r="AY25" s="44" t="s">
-        <x:v>96</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="AZ25" s="44"/>
       <x:c r="BA25" s="44"/>
       <x:c r="BB25" s="44" t="s">
-        <x:v>293</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="BC25" s="44"/>
       <x:c r="BD25" s="44"/>
@@ -5915,7 +6247,7 @@
         <x:v>231</x:v>
       </x:c>
       <x:c r="BH25" s="44" t="s">
-        <x:v>93</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="BI25" s="44"/>
       <x:c r="BJ25" s="44" t="s">
@@ -5928,10 +6260,10 @@
         <x:v>121</x:v>
       </x:c>
       <x:c r="C26" s="44" t="s">
-        <x:v>68</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="D26" s="44" t="s">
-        <x:v>184</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="E26" s="44" t="s">
         <x:v>78</x:v>
@@ -5940,22 +6272,22 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="G26" s="44" t="s">
-        <x:v>81</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="H26" s="44" t="s">
-        <x:v>206</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="I26" s="44" t="s">
-        <x:v>83</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="J26" s="44" t="s">
-        <x:v>296</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="K26" s="44" t="s">
-        <x:v>209</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="L26" s="44" t="s">
-        <x:v>82</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="M26" s="44" t="s">
         <x:v>183</x:v>
@@ -5973,22 +6305,22 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="R26" s="46" t="s">
-        <x:v>266</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="S26" s="44" t="s">
-        <x:v>71</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="T26" s="44" t="s">
-        <x:v>209</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="U26" s="44" t="s">
-        <x:v>301</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="V26" s="44" t="s">
         <x:v>251</x:v>
       </x:c>
       <x:c r="W26" s="44" t="s">
-        <x:v>302</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="X26" s="44" t="s">
         <x:v>110</x:v>
@@ -5997,16 +6329,16 @@
         <x:v>125</x:v>
       </x:c>
       <x:c r="Z26" s="44" t="s">
-        <x:v>303</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="AA26" s="44" t="s">
-        <x:v>304</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="AB26" s="44" t="s">
-        <x:v>304</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="AC26" s="44" t="s">
-        <x:v>305</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="AD26" s="44" t="s">
         <x:v>127</x:v>
@@ -6018,26 +6350,26 @@
         <x:v>129</x:v>
       </x:c>
       <x:c r="AG26" s="44" t="s">
-        <x:v>298</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="AH26" s="44" t="s">
-        <x:v>299</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="AI26" s="44" t="s">
-        <x:v>254</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="AJ26" s="44" t="s">
-        <x:v>306</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="AK26" s="44" t="s">
         <x:v>152</x:v>
       </x:c>
       <x:c r="AL26" s="44" t="s">
-        <x:v>307</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="AM26" s="44"/>
       <x:c r="AN26" s="44" t="s">
-        <x:v>308</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="AO26" s="44" t="s">
         <x:v>155</x:v>
@@ -6062,9 +6394,11 @@
       <x:c r="AW26" s="44" t="s">
         <x:v>199</x:v>
       </x:c>
-      <x:c r="AX26" s="44"/>
+      <x:c r="AX26" s="44" t="s">
+        <x:v>339</x:v>
+      </x:c>
       <x:c r="AY26" s="44" t="s">
-        <x:v>141</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="AZ26" s="44" t="s">
         <x:v>93</x:v>
@@ -6081,7 +6415,7 @@
         <x:v>231</x:v>
       </x:c>
       <x:c r="BH26" s="44" t="s">
-        <x:v>164</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="BI26" s="44"/>
       <x:c r="BJ26" s="44" t="s">
@@ -6093,18 +6427,32 @@
       <x:c r="B27" s="36" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="C27" s="44"/>
-      <x:c r="D27" s="44"/>
+      <x:c r="C27" s="44" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="D27" s="44" t="s">
+        <x:v>342</x:v>
+      </x:c>
       <x:c r="E27" s="44"/>
       <x:c r="F27" s="44"/>
-      <x:c r="G27" s="44"/>
-      <x:c r="H27" s="44"/>
-      <x:c r="I27" s="44"/>
-      <x:c r="J27" s="44"/>
+      <x:c r="G27" s="44" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="H27" s="44" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="I27" s="44" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="J27" s="44" t="s">
+        <x:v>322</x:v>
+      </x:c>
       <x:c r="K27" s="44" t="s">
-        <x:v>309</x:v>
-      </x:c>
-      <x:c r="L27" s="44"/>
+        <x:v>344</x:v>
+      </x:c>
+      <x:c r="L27" s="44" t="s">
+        <x:v>345</x:v>
+      </x:c>
       <x:c r="M27" s="44"/>
       <x:c r="N27" s="44"/>
       <x:c r="O27" s="44"/>
@@ -6112,22 +6460,28 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="Q27" s="44" t="s">
-        <x:v>310</x:v>
-      </x:c>
-      <x:c r="R27" s="44"/>
-      <x:c r="S27" s="44"/>
-      <x:c r="T27" s="44"/>
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="R27" s="44" t="s">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c r="S27" s="44" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="T27" s="44" t="s">
+        <x:v>348</x:v>
+      </x:c>
       <x:c r="U27" s="44" t="s">
-        <x:v>269</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="V27" s="44"/>
       <x:c r="W27" s="44" t="s">
-        <x:v>311</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="X27" s="44"/>
       <x:c r="Y27" s="44"/>
       <x:c r="Z27" s="44" t="s">
-        <x:v>312</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="AA27" s="44" t="s">
         <x:v>89</x:v>
@@ -6143,17 +6497,19 @@
       <x:c r="AF27" s="44"/>
       <x:c r="AG27" s="44"/>
       <x:c r="AH27" s="44" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="AI27" s="44"/>
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="AI27" s="44" t="s">
+        <x:v>350</x:v>
+      </x:c>
       <x:c r="AJ27" s="44" t="s">
-        <x:v>71</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="AK27" s="44" t="s">
         <x:v>152</x:v>
       </x:c>
       <x:c r="AL27" s="44" t="s">
-        <x:v>313</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="AM27" s="44" t="s">
         <x:v>153</x:v>
@@ -6165,7 +6521,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="AP27" s="44" t="s">
-        <x:v>314</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="AQ27" s="44" t="s">
         <x:v>158</x:v>
@@ -6175,7 +6531,7 @@
       </x:c>
       <x:c r="AS27" s="44"/>
       <x:c r="AT27" s="44" t="s">
-        <x:v>315</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="AU27" s="44" t="s">
         <x:v>95</x:v>
@@ -6184,13 +6540,13 @@
         <x:v>199</x:v>
       </x:c>
       <x:c r="AW27" s="44" t="s">
-        <x:v>316</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="AX27" s="44" t="s">
-        <x:v>83</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="AY27" s="44" t="s">
-        <x:v>277</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="AZ27" s="44" t="s">
         <x:v>86</x:v>
@@ -6202,22 +6558,22 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="BC27" s="44" t="s">
-        <x:v>317</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="BD27" s="44" t="s">
-        <x:v>318</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="BE27" s="44" t="s">
-        <x:v>318</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="BF27" s="44" t="s">
-        <x:v>319</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="BG27" s="44" t="s">
-        <x:v>320</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="BH27" s="44" t="s">
-        <x:v>141</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="BI27" s="44"/>
       <x:c r="BJ27" s="44"/>
@@ -6227,29 +6583,55 @@
       <x:c r="B28" s="36" t="s">
         <x:v>165</x:v>
       </x:c>
-      <x:c r="C28" s="44"/>
-      <x:c r="D28" s="44"/>
+      <x:c r="C28" s="44" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="D28" s="44" t="s">
+        <x:v>322</x:v>
+      </x:c>
       <x:c r="E28" s="44"/>
       <x:c r="F28" s="44"/>
-      <x:c r="G28" s="44"/>
-      <x:c r="H28" s="44"/>
-      <x:c r="I28" s="44"/>
-      <x:c r="J28" s="44"/>
-      <x:c r="K28" s="44"/>
-      <x:c r="L28" s="44"/>
+      <x:c r="G28" s="44" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="H28" s="44" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="I28" s="44" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="J28" s="44" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="K28" s="44" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="L28" s="44" t="s">
+        <x:v>322</x:v>
+      </x:c>
       <x:c r="M28" s="44"/>
       <x:c r="N28" s="44"/>
       <x:c r="O28" s="44"/>
       <x:c r="P28" s="44"/>
       <x:c r="Q28" s="44" t="s">
-        <x:v>321</x:v>
-      </x:c>
-      <x:c r="R28" s="44"/>
-      <x:c r="S28" s="44"/>
-      <x:c r="T28" s="44"/>
-      <x:c r="U28" s="44"/>
+        <x:v>362</x:v>
+      </x:c>
+      <x:c r="R28" s="44" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="S28" s="44" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="T28" s="44" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="U28" s="44" t="s">
+        <x:v>322</x:v>
+      </x:c>
       <x:c r="V28" s="44"/>
-      <x:c r="W28" s="44"/>
+      <x:c r="W28" s="44" t="s">
+        <x:v>322</x:v>
+      </x:c>
       <x:c r="X28" s="44"/>
       <x:c r="Y28" s="44"/>
       <x:c r="Z28" s="44"/>
@@ -6260,15 +6642,21 @@
       <x:c r="AE28" s="44"/>
       <x:c r="AF28" s="44"/>
       <x:c r="AG28" s="44"/>
-      <x:c r="AH28" s="44"/>
-      <x:c r="AI28" s="44"/>
+      <x:c r="AH28" s="44" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="AI28" s="44" t="s">
+        <x:v>322</x:v>
+      </x:c>
       <x:c r="AJ28" s="44" t="s">
-        <x:v>153</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="AK28" s="44" t="s">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="AL28" s="44"/>
+      <x:c r="AL28" s="44" t="s">
+        <x:v>322</x:v>
+      </x:c>
       <x:c r="AM28" s="44" t="s">
         <x:v>167</x:v>
       </x:c>
@@ -6277,7 +6665,7 @@
       </x:c>
       <x:c r="AO28" s="44"/>
       <x:c r="AP28" s="44" t="s">
-        <x:v>314</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="AQ28" s="44" t="s">
         <x:v>171</x:v>
@@ -6291,15 +6679,17 @@
         <x:v>158</x:v>
       </x:c>
       <x:c r="AV28" s="44" t="s">
-        <x:v>316</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="AW28" s="44" t="s">
         <x:v>119</x:v>
       </x:c>
       <x:c r="AX28" s="44" t="s">
-        <x:v>277</x:v>
-      </x:c>
-      <x:c r="AY28" s="44"/>
+        <x:v>364</x:v>
+      </x:c>
+      <x:c r="AY28" s="44" t="s">
+        <x:v>322</x:v>
+      </x:c>
       <x:c r="AZ28" s="44" t="s">
         <x:v>86</x:v>
       </x:c>
@@ -6308,19 +6698,21 @@
       </x:c>
       <x:c r="BB28" s="44"/>
       <x:c r="BC28" s="44" t="s">
-        <x:v>317</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="BD28" s="44" t="s">
-        <x:v>318</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="BE28" s="44" t="s">
-        <x:v>318</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="BF28" s="44" t="s">
-        <x:v>319</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="BG28" s="44"/>
-      <x:c r="BH28" s="44"/>
+      <x:c r="BH28" s="44" t="s">
+        <x:v>322</x:v>
+      </x:c>
       <x:c r="BI28" s="44" t="s">
         <x:v>141</x:v>
       </x:c>
@@ -6331,27 +6723,53 @@
       <x:c r="B29" s="36" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="C29" s="44"/>
-      <x:c r="D29" s="44"/>
+      <x:c r="C29" s="44" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="D29" s="44" t="s">
+        <x:v>322</x:v>
+      </x:c>
       <x:c r="E29" s="44"/>
       <x:c r="F29" s="44"/>
-      <x:c r="G29" s="44"/>
-      <x:c r="H29" s="44"/>
-      <x:c r="I29" s="44"/>
-      <x:c r="J29" s="44"/>
-      <x:c r="K29" s="44"/>
-      <x:c r="L29" s="44"/>
+      <x:c r="G29" s="44" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="H29" s="44" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="I29" s="44" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="J29" s="44" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="K29" s="44" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="L29" s="44" t="s">
+        <x:v>322</x:v>
+      </x:c>
       <x:c r="M29" s="44"/>
       <x:c r="N29" s="44"/>
       <x:c r="O29" s="44"/>
       <x:c r="P29" s="44"/>
       <x:c r="Q29" s="44"/>
-      <x:c r="R29" s="44"/>
-      <x:c r="S29" s="44"/>
-      <x:c r="T29" s="44"/>
-      <x:c r="U29" s="44"/>
+      <x:c r="R29" s="44" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="S29" s="44" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="T29" s="44" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="U29" s="44" t="s">
+        <x:v>322</x:v>
+      </x:c>
       <x:c r="V29" s="44"/>
-      <x:c r="W29" s="44"/>
+      <x:c r="W29" s="44" t="s">
+        <x:v>322</x:v>
+      </x:c>
       <x:c r="X29" s="44"/>
       <x:c r="Y29" s="44"/>
       <x:c r="Z29" s="44"/>
@@ -6362,22 +6780,30 @@
       <x:c r="AE29" s="44"/>
       <x:c r="AF29" s="44"/>
       <x:c r="AG29" s="44"/>
-      <x:c r="AH29" s="44"/>
-      <x:c r="AI29" s="44"/>
-      <x:c r="AJ29" s="44"/>
+      <x:c r="AH29" s="44" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="AI29" s="44" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="AJ29" s="44" t="s">
+        <x:v>322</x:v>
+      </x:c>
       <x:c r="AK29" s="44"/>
-      <x:c r="AL29" s="44"/>
+      <x:c r="AL29" s="44" t="s">
+        <x:v>322</x:v>
+      </x:c>
       <x:c r="AM29" s="44" t="s">
         <x:v>167</x:v>
       </x:c>
       <x:c r="AN29" s="44"/>
       <x:c r="AO29" s="44"/>
       <x:c r="AP29" s="44" t="s">
-        <x:v>314</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="AQ29" s="44"/>
       <x:c r="AR29" s="44" t="s">
-        <x:v>322</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="AS29" s="44"/>
       <x:c r="AT29" s="44"/>
@@ -6385,9 +6811,11 @@
       <x:c r="AV29" s="44"/>
       <x:c r="AW29" s="44"/>
       <x:c r="AX29" s="44" t="s">
-        <x:v>281</x:v>
-      </x:c>
-      <x:c r="AY29" s="44"/>
+        <x:v>366</x:v>
+      </x:c>
+      <x:c r="AY29" s="44" t="s">
+        <x:v>322</x:v>
+      </x:c>
       <x:c r="AZ29" s="44"/>
       <x:c r="BA29" s="44" t="s">
         <x:v>238</x:v>
@@ -6397,16 +6825,18 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="BD29" s="44" t="s">
-        <x:v>323</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="BE29" s="44" t="s">
-        <x:v>323</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="BF29" s="44" t="s">
         <x:v>231</x:v>
       </x:c>
       <x:c r="BG29" s="44"/>
-      <x:c r="BH29" s="44"/>
+      <x:c r="BH29" s="44" t="s">
+        <x:v>322</x:v>
+      </x:c>
       <x:c r="BI29" s="44" t="s">
         <x:v>86</x:v>
       </x:c>
@@ -6414,7 +6844,7 @@
     </x:row>
     <x:row r="30" spans="1:62" ht="76.5" customHeight="1">
       <x:c r="A30" s="37" t="s">
-        <x:v>324</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="B30" s="38" t="s">
         <x:v>67</x:v>
@@ -6435,7 +6865,7 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="H30" s="39" t="s">
-        <x:v>286</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="I30" s="39" t="s">
         <x:v>258</x:v>
@@ -6447,7 +6877,7 @@
         <x:v>208</x:v>
       </x:c>
       <x:c r="L30" s="39" t="s">
-        <x:v>296</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="M30" s="39" t="s">
         <x:v>80</x:v>
@@ -6472,7 +6902,7 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="W30" s="39" t="s">
-        <x:v>302</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="X30" s="39" t="s">
         <x:v>198</x:v>
@@ -6489,7 +6919,7 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="AD30" s="39" t="s">
-        <x:v>325</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="AE30" s="39"/>
       <x:c r="AF30" s="39" t="s">
@@ -6497,7 +6927,7 @@
       </x:c>
       <x:c r="AG30" s="39"/>
       <x:c r="AH30" s="39" t="s">
-        <x:v>326</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="AI30" s="39"/>
       <x:c r="AJ30" s="39"/>
@@ -6514,7 +6944,7 @@
       <x:c r="AS30" s="39"/>
       <x:c r="AT30" s="39"/>
       <x:c r="AU30" s="39" t="s">
-        <x:v>327</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="AV30" s="41" t="s">
         <x:v>150</x:v>
@@ -6534,7 +6964,7 @@
       <x:c r="BE30" s="39"/>
       <x:c r="BF30" s="39"/>
       <x:c r="BG30" s="39" t="s">
-        <x:v>319</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="BH30" s="39"/>
       <x:c r="BI30" s="39" t="s">
@@ -6559,13 +6989,13 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="F31" s="39" t="s">
-        <x:v>328</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="G31" s="39" t="s">
         <x:v>206</x:v>
       </x:c>
       <x:c r="H31" s="39" t="s">
-        <x:v>329</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="I31" s="39" t="s">
         <x:v>208</x:v>
@@ -6574,7 +7004,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="K31" s="39" t="s">
-        <x:v>296</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="L31" s="39" t="s">
         <x:v>77</x:v>
@@ -6607,16 +7037,16 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="V31" s="39" t="s">
-        <x:v>289</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="W31" s="39" t="s">
-        <x:v>311</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="X31" s="39" t="s">
         <x:v>71</x:v>
       </x:c>
       <x:c r="Y31" s="39" t="s">
-        <x:v>330</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="Z31" s="39" t="s">
         <x:v>212</x:v>
@@ -6631,10 +7061,10 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="AD31" s="39" t="s">
-        <x:v>331</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="AE31" s="39" t="s">
-        <x:v>325</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="AF31" s="39" t="s">
         <x:v>86</x:v>
@@ -6646,7 +7076,7 @@
         <x:v>116</x:v>
       </x:c>
       <x:c r="AI31" s="39" t="s">
-        <x:v>326</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="AJ31" s="39"/>
       <x:c r="AK31" s="39"/>
@@ -6666,7 +7096,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="AU31" s="39" t="s">
-        <x:v>327</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="AV31" s="39" t="s">
         <x:v>137</x:v>
@@ -6688,7 +7118,7 @@
       <x:c r="BE31" s="39"/>
       <x:c r="BF31" s="39"/>
       <x:c r="BG31" s="39" t="s">
-        <x:v>294</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="BH31" s="39"/>
       <x:c r="BI31" s="39" t="s">
@@ -6710,7 +7140,7 @@
         <x:v>185</x:v>
       </x:c>
       <x:c r="E32" s="39" t="s">
-        <x:v>328</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="F32" s="39" t="s">
         <x:v>81</x:v>
@@ -6725,7 +7155,7 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="J32" s="39" t="s">
-        <x:v>296</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="K32" s="39" t="s">
         <x:v>102</x:v>
@@ -6740,7 +7170,7 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="O32" s="39" t="s">
-        <x:v>329</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="P32" s="39" t="s">
         <x:v>76</x:v>
@@ -6765,13 +7195,13 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="X32" s="39" t="s">
-        <x:v>330</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="Y32" s="39" t="s">
-        <x:v>332</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="Z32" s="39" t="s">
-        <x:v>333</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="AA32" s="39" t="s">
         <x:v>127</x:v>
@@ -6786,16 +7216,16 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="AE32" s="39" t="s">
-        <x:v>331</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="AF32" s="39" t="s">
-        <x:v>334</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="AG32" s="39" t="s">
-        <x:v>334</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="AH32" s="39" t="s">
-        <x:v>335</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="AI32" s="39" t="s">
         <x:v>116</x:v>
@@ -6811,7 +7241,7 @@
         <x:v>153</x:v>
       </x:c>
       <x:c r="AN32" s="39" t="s">
-        <x:v>308</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="AO32" s="39" t="s">
         <x:v>155</x:v>
@@ -6831,17 +7261,17 @@
         <x:v>203</x:v>
       </x:c>
       <x:c r="AV32" s="39" t="s">
-        <x:v>336</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="AW32" s="39" t="s">
-        <x:v>336</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="AX32" s="39" t="s">
         <x:v>141</x:v>
       </x:c>
       <x:c r="AY32" s="41"/>
       <x:c r="AZ32" s="39" t="s">
-        <x:v>337</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="BA32" s="41" t="s">
         <x:v>118</x:v>
@@ -6877,7 +7307,7 @@
       <x:c r="H33" s="39"/>
       <x:c r="I33" s="39"/>
       <x:c r="J33" s="39" t="s">
-        <x:v>338</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="K33" s="39"/>
       <x:c r="L33" s="41" t="s">
@@ -6890,17 +7320,17 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="O33" s="39" t="s">
-        <x:v>339</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="P33" s="39" t="s">
-        <x:v>340</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="Q33" s="39"/>
       <x:c r="R33" s="39" t="s">
-        <x:v>286</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="S33" s="39" t="s">
-        <x:v>286</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="T33" s="39"/>
       <x:c r="U33" s="39"/>
@@ -6925,10 +7355,10 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="AH33" s="41" t="s">
-        <x:v>341</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="AI33" s="39" t="s">
-        <x:v>335</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="AJ33" s="39" t="s">
         <x:v>275</x:v>
@@ -6947,13 +7377,13 @@
         <x:v>155</x:v>
       </x:c>
       <x:c r="AP33" s="39" t="s">
-        <x:v>314</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="AQ33" s="39" t="s">
         <x:v>246</x:v>
       </x:c>
       <x:c r="AR33" s="39" t="s">
-        <x:v>342</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="AS33" s="39" t="s">
         <x:v>199</x:v>
@@ -6963,10 +7393,10 @@
       </x:c>
       <x:c r="AU33" s="39"/>
       <x:c r="AV33" s="39" t="s">
-        <x:v>343</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="AW33" s="39" t="s">
-        <x:v>343</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="AX33" s="39" t="s">
         <x:v>220</x:v>
@@ -6983,13 +7413,13 @@
       <x:c r="BB33" s="39"/>
       <x:c r="BC33" s="39"/>
       <x:c r="BD33" s="39" t="s">
-        <x:v>344</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="BE33" s="39" t="s">
         <x:v>178</x:v>
       </x:c>
       <x:c r="BF33" s="39" t="s">
-        <x:v>319</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="BG33" s="39"/>
       <x:c r="BH33" s="39" t="s">
@@ -7053,10 +7483,10 @@
       <x:c r="AN34" s="39"/>
       <x:c r="AO34" s="39"/>
       <x:c r="AP34" s="39" t="s">
-        <x:v>314</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="AQ34" s="39" t="s">
-        <x:v>345</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="AR34" s="39" t="s">
         <x:v>276</x:v>
@@ -7081,7 +7511,7 @@
         <x:v>230</x:v>
       </x:c>
       <x:c r="BB34" s="39" t="s">
-        <x:v>346</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="BC34" s="39"/>
       <x:c r="BD34" s="39" t="s">
@@ -7151,7 +7581,7 @@
       <x:c r="AN35" s="39"/>
       <x:c r="AO35" s="39"/>
       <x:c r="AP35" s="39" t="s">
-        <x:v>314</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="AQ35" s="39"/>
       <x:c r="AR35" s="39" t="s">
@@ -7171,14 +7601,14 @@
         <x:v>230</x:v>
       </x:c>
       <x:c r="BB35" s="39" t="s">
-        <x:v>317</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="BC35" s="39"/>
       <x:c r="BD35" s="39" t="s">
-        <x:v>317</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="BE35" s="39" t="s">
-        <x:v>317</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="BF35" s="39" t="s">
         <x:v>231</x:v>
@@ -7192,7 +7622,7 @@
     </x:row>
     <x:row r="36" spans="1:62" ht="76.5" customHeight="1">
       <x:c r="A36" s="43" t="s">
-        <x:v>347</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="B36" s="36" t="s">
         <x:v>67</x:v>
@@ -7210,7 +7640,7 @@
         <x:v>193</x:v>
       </x:c>
       <x:c r="G36" s="44" t="s">
-        <x:v>348</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="H36" s="44"/>
       <x:c r="I36" s="44" t="s">
@@ -7245,7 +7675,7 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="T36" s="44" t="s">
-        <x:v>288</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="U36" s="44" t="s">
         <x:v>78</x:v>
@@ -7254,16 +7684,16 @@
         <x:v>251</x:v>
       </x:c>
       <x:c r="W36" s="44" t="s">
-        <x:v>349</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="X36" s="44" t="s">
         <x:v>87</x:v>
       </x:c>
       <x:c r="Y36" s="44" t="s">
-        <x:v>330</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="Z36" s="44" t="s">
-        <x:v>307</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="AA36" s="44"/>
       <x:c r="AB36" s="44" t="s">
@@ -7291,7 +7721,7 @@
       <x:c r="AN36" s="44"/>
       <x:c r="AO36" s="44"/>
       <x:c r="AP36" s="44" t="s">
-        <x:v>314</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="AQ36" s="44"/>
       <x:c r="AR36" s="44"/>
@@ -7301,7 +7731,7 @@
         <x:v>227</x:v>
       </x:c>
       <x:c r="AV36" s="44" t="s">
-        <x:v>316</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="AW36" s="44"/>
       <x:c r="AX36" s="44"/>
@@ -7331,10 +7761,10 @@
         <x:v>184</x:v>
       </x:c>
       <x:c r="D37" s="44" t="s">
-        <x:v>350</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="E37" s="44" t="s">
-        <x:v>348</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="F37" s="44" t="s">
         <x:v>103</x:v>
@@ -7373,7 +7803,7 @@
         <x:v>199</x:v>
       </x:c>
       <x:c r="R37" s="44" t="s">
-        <x:v>351</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="S37" s="44" t="s">
         <x:v>104</x:v>
@@ -7391,7 +7821,7 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="X37" s="44" t="s">
-        <x:v>307</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="Y37" s="44" t="s">
         <x:v>87</x:v>
@@ -7400,22 +7830,22 @@
         <x:v>168</x:v>
       </x:c>
       <x:c r="AA37" s="44" t="s">
-        <x:v>352</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="AB37" s="44" t="s">
-        <x:v>352</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="AC37" s="44" t="s">
         <x:v>215</x:v>
       </x:c>
       <x:c r="AD37" s="44" t="s">
-        <x:v>353</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="AE37" s="44" t="s">
-        <x:v>331</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="AF37" s="44" t="s">
-        <x:v>298</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="AG37" s="44"/>
       <x:c r="AH37" s="44" t="s">
@@ -7435,22 +7865,22 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="AP37" s="44" t="s">
-        <x:v>314</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="AQ37" s="44"/>
       <x:c r="AR37" s="44"/>
       <x:c r="AS37" s="44"/>
       <x:c r="AT37" s="44" t="s">
-        <x:v>354</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="AU37" s="44" t="s">
         <x:v>203</x:v>
       </x:c>
       <x:c r="AV37" s="44" t="s">
-        <x:v>355</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="AW37" s="44" t="s">
-        <x:v>355</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="AX37" s="44"/>
       <x:c r="AY37" s="44"/>
@@ -7478,7 +7908,7 @@
         <x:v>121</x:v>
       </x:c>
       <x:c r="C38" s="44" t="s">
-        <x:v>350</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="D38" s="44" t="s">
         <x:v>122</x:v>
@@ -7487,7 +7917,7 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="F38" s="44" t="s">
-        <x:v>348</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="G38" s="44" t="s">
         <x:v>71</x:v>
@@ -7526,7 +7956,7 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="S38" s="44" t="s">
-        <x:v>351</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="T38" s="44" t="s">
         <x:v>108</x:v>
@@ -7538,16 +7968,16 @@
         <x:v>109</x:v>
       </x:c>
       <x:c r="W38" s="44" t="s">
-        <x:v>302</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="X38" s="44" t="s">
-        <x:v>330</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="Y38" s="44" t="s">
-        <x:v>307</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="Z38" s="44" t="s">
-        <x:v>356</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="AA38" s="44" t="s">
         <x:v>215</x:v>
@@ -7559,16 +7989,16 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="AD38" s="44" t="s">
-        <x:v>331</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="AE38" s="44" t="s">
-        <x:v>353</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="AF38" s="44" t="s">
         <x:v>91</x:v>
       </x:c>
       <x:c r="AG38" s="44" t="s">
-        <x:v>298</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="AH38" s="44" t="s">
         <x:v>254</x:v>
@@ -7589,24 +8019,24 @@
         <x:v>233</x:v>
       </x:c>
       <x:c r="AP38" s="44" t="s">
-        <x:v>314</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="AQ38" s="44"/>
       <x:c r="AR38" s="44"/>
       <x:c r="AS38" s="44" t="s">
-        <x:v>357</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="AT38" s="44" t="s">
         <x:v>203</x:v>
       </x:c>
       <x:c r="AU38" s="44" t="s">
-        <x:v>354</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="AV38" s="44" t="s">
-        <x:v>358</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="AW38" s="44" t="s">
-        <x:v>358</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="AX38" s="44" t="s">
         <x:v>220</x:v>
@@ -7682,7 +8112,7 @@
         <x:v>153</x:v>
       </x:c>
       <x:c r="AK39" s="44" t="s">
-        <x:v>359</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="AL39" s="44" t="s">
         <x:v>132</x:v>
@@ -7702,7 +8132,7 @@
         <x:v>156</x:v>
       </x:c>
       <x:c r="AS39" s="44" t="s">
-        <x:v>360</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="AT39" s="44" t="s">
         <x:v>227</x:v>
@@ -7710,7 +8140,7 @@
       <x:c r="AU39" s="44"/>
       <x:c r="AV39" s="44"/>
       <x:c r="AW39" s="44" t="s">
-        <x:v>316</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="AX39" s="44" t="s">
         <x:v>219</x:v>
@@ -7739,7 +8169,7 @@
       </x:c>
       <x:c r="BI39" s="44"/>
       <x:c r="BJ39" s="44" t="s">
-        <x:v>361</x:v>
+        <x:v>410</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:62" ht="51" customHeight="1">
@@ -7802,7 +8232,7 @@
         <x:v>156</x:v>
       </x:c>
       <x:c r="AS40" s="44" t="s">
-        <x:v>360</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="AT40" s="44"/>
       <x:c r="AU40" s="44"/>
@@ -7833,7 +8263,7 @@
       <x:c r="BH40" s="44"/>
       <x:c r="BI40" s="44"/>
       <x:c r="BJ40" s="44" t="s">
-        <x:v>361</x:v>
+        <x:v>410</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:62" ht="51" customHeight="1">
@@ -7921,7 +8351,7 @@
       <x:c r="BH41" s="44"/>
       <x:c r="BI41" s="44"/>
       <x:c r="BJ41" s="44" t="s">
-        <x:v>361</x:v>
+        <x:v>410</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:62" ht="12" customHeight="1"/>
@@ -7973,7 +8403,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{c8b76d27-8cdf-4ed3-9116-8b4b43be7c98}" mc:Ignorable="x14ac xr xr2 xr3">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{28936f8e-f48a-41c7-92e7-e7e4ebc0be9a}" mc:Ignorable="x14ac xr xr2 xr3">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -7982,7 +8412,7 @@
   <x:sheetData>
     <x:row r="5" spans="1:1" ht="23.25" customHeight="1">
       <x:c r="A5" s="48" t="s">
-        <x:v>362</x:v>
+        <x:v>411</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
